--- a/base.xlsx
+++ b/base.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb4504e36c3967e3/Desktop/PAINEIS/Base/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb4504e36c3967e3/Desktop/PAINEIS/Base/SISTEMA/sistema-patrimonial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{0F039CA3-B950-45CF-99D7-979372707199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D101C96-9B16-45C0-A507-57AC22C19575}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{0F039CA3-B950-45CF-99D7-979372707199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A413F354-53DD-44B2-BDF5-E508F9C230D2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F92458B9-4278-486E-A3B1-73089C24882F}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="211">
   <si>
     <t>GRUPO</t>
   </si>
@@ -673,6 +673,15 @@
   </si>
   <si>
     <t>NXGMFAL006741169E5A9501</t>
+  </si>
+  <si>
+    <t>Optical Power meter</t>
+  </si>
+  <si>
+    <t>Cablix</t>
+  </si>
+  <si>
+    <t>TPN-35</t>
   </si>
 </sst>
 </file>
@@ -683,7 +692,7 @@
     <numFmt numFmtId="6" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -718,6 +727,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -740,7 +755,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -789,6 +804,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -987,8 +1005,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{54F51857-5AFF-4C8D-BC81-560A3E6C8471}" name="Tabela1" displayName="Tabela1" ref="A1:Q75" headerRowDxfId="38" dataDxfId="37">
-  <autoFilter ref="A1:Q75" xr:uid="{54F51857-5AFF-4C8D-BC81-560A3E6C8471}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{54F51857-5AFF-4C8D-BC81-560A3E6C8471}" name="Tabela1" displayName="Tabela1" ref="A1:Q102" headerRowDxfId="38" dataDxfId="37">
+  <autoFilter ref="A1:Q102" xr:uid="{54F51857-5AFF-4C8D-BC81-560A3E6C8471}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q59">
     <sortCondition ref="A2:A59"/>
   </sortState>
@@ -1354,11 +1372,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048A3243-A81D-43E0-B388-E3A8FF5A2F97}">
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="79" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.77734375" bestFit="1" customWidth="1"/>
@@ -5097,7 +5115,1358 @@
       </c>
       <c r="Q75" s="9"/>
     </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A76" s="9">
+        <v>157</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E76" s="18">
+        <v>202503080103</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I76" s="6">
+        <v>1</v>
+      </c>
+      <c r="J76" s="7">
+        <v>600</v>
+      </c>
+      <c r="K76" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L76" s="6"/>
+      <c r="M76" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N76" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O76" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P76" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q76" s="9"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A77" s="9">
+        <v>158</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E77" s="18">
+        <v>202503080152</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I77" s="6">
+        <v>1</v>
+      </c>
+      <c r="J77" s="7">
+        <v>600</v>
+      </c>
+      <c r="K77" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L77" s="6"/>
+      <c r="M77" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O77" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P77" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q77" s="9"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A78" s="9">
+        <v>159</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E78" s="18">
+        <v>202503080124</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I78" s="6">
+        <v>1</v>
+      </c>
+      <c r="J78" s="7">
+        <v>600</v>
+      </c>
+      <c r="K78" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L78" s="6"/>
+      <c r="M78" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O78" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P78" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q78" s="9"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A79" s="9">
+        <v>165</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E79" s="18">
+        <v>202503080253</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I79" s="6">
+        <v>1</v>
+      </c>
+      <c r="J79" s="7">
+        <v>600</v>
+      </c>
+      <c r="K79" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L79" s="6"/>
+      <c r="M79" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O79" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P79" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q79" s="9"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A80" s="9">
+        <v>160</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E80" s="18">
+        <v>202503080082</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I80" s="6">
+        <v>1</v>
+      </c>
+      <c r="J80" s="7">
+        <v>600</v>
+      </c>
+      <c r="K80" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L80" s="6"/>
+      <c r="M80" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N80" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O80" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P80" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q80" s="9"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A81" s="9">
+        <v>164</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="18">
+        <v>202503080017</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I81" s="6">
+        <v>1</v>
+      </c>
+      <c r="J81" s="7">
+        <v>600</v>
+      </c>
+      <c r="K81" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L81" s="6"/>
+      <c r="M81" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N81" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O81" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P81" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q81" s="9"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A82" s="9">
+        <v>161</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E82" s="18">
+        <v>202503080068</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I82" s="6">
+        <v>1</v>
+      </c>
+      <c r="J82" s="7">
+        <v>600</v>
+      </c>
+      <c r="K82" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L82" s="6"/>
+      <c r="M82" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N82" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O82" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P82" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q82" s="9"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A83" s="9">
+        <v>162</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E83" s="18">
+        <v>202503080292</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I83" s="6">
+        <v>1</v>
+      </c>
+      <c r="J83" s="7">
+        <v>600</v>
+      </c>
+      <c r="K83" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L83" s="6"/>
+      <c r="M83" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N83" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P83" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q83" s="9"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A84" s="9">
+        <v>163</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E84" s="18">
+        <v>202503080143</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" s="6">
+        <v>1</v>
+      </c>
+      <c r="J84" s="7">
+        <v>600</v>
+      </c>
+      <c r="K84" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L84" s="6"/>
+      <c r="M84" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N84" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O84" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P84" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q84" s="9"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A85" s="9">
+        <v>166</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E85" s="18">
+        <v>202503080227</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I85" s="6">
+        <v>1</v>
+      </c>
+      <c r="J85" s="7">
+        <v>600</v>
+      </c>
+      <c r="K85" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L85" s="6"/>
+      <c r="M85" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N85" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O85" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P85" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q85" s="9"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A86" s="9">
+        <v>167</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E86" s="18">
+        <v>202503080265</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I86" s="6">
+        <v>1</v>
+      </c>
+      <c r="J86" s="7">
+        <v>600</v>
+      </c>
+      <c r="K86" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L86" s="6"/>
+      <c r="M86" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N86" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O86" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P86" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q86" s="9"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A87" s="9">
+        <v>168</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E87" s="18">
+        <v>202503080118</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87" s="6">
+        <v>1</v>
+      </c>
+      <c r="J87" s="7">
+        <v>600</v>
+      </c>
+      <c r="K87" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L87" s="6"/>
+      <c r="M87" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N87" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O87" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P87" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q87" s="9"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A88" s="9">
+        <v>169</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E88" s="18">
+        <v>202503080066</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" s="6">
+        <v>1</v>
+      </c>
+      <c r="J88" s="7">
+        <v>600</v>
+      </c>
+      <c r="K88" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L88" s="6"/>
+      <c r="M88" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N88" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O88" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P88" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q88" s="9"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A89" s="9">
+        <v>170</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E89" s="18">
+        <v>202503080263</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" s="6">
+        <v>1</v>
+      </c>
+      <c r="J89" s="7">
+        <v>600</v>
+      </c>
+      <c r="K89" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L89" s="6"/>
+      <c r="M89" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N89" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O89" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P89" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q89" s="9"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A90" s="9">
+        <v>171</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E90" s="18">
+        <v>202503080138</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" s="6">
+        <v>1</v>
+      </c>
+      <c r="J90" s="7">
+        <v>600</v>
+      </c>
+      <c r="K90" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L90" s="6"/>
+      <c r="M90" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N90" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O90" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P90" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q90" s="9"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A91" s="9">
+        <v>172</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E91" s="18">
+        <v>202503080071</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I91" s="6">
+        <v>1</v>
+      </c>
+      <c r="J91" s="7">
+        <v>600</v>
+      </c>
+      <c r="K91" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L91" s="6"/>
+      <c r="M91" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N91" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O91" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P91" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q91" s="9"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A92" s="9">
+        <v>173</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E92" s="18">
+        <v>202503080131</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I92" s="6">
+        <v>1</v>
+      </c>
+      <c r="J92" s="7">
+        <v>600</v>
+      </c>
+      <c r="K92" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L92" s="6"/>
+      <c r="M92" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N92" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O92" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P92" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q92" s="9"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A93" s="9">
+        <v>174</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E93" s="18">
+        <v>202503080268</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I93" s="6">
+        <v>1</v>
+      </c>
+      <c r="J93" s="7">
+        <v>600</v>
+      </c>
+      <c r="K93" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L93" s="6"/>
+      <c r="M93" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N93" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O93" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P93" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q93" s="9"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A94" s="9">
+        <v>175</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E94" s="18">
+        <v>202503080164</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I94" s="6">
+        <v>1</v>
+      </c>
+      <c r="J94" s="7">
+        <v>600</v>
+      </c>
+      <c r="K94" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L94" s="6"/>
+      <c r="M94" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N94" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O94" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P94" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q94" s="9"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A95" s="9">
+        <v>176</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E95" s="18">
+        <v>202503080122</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" s="6">
+        <v>1</v>
+      </c>
+      <c r="J95" s="7">
+        <v>600</v>
+      </c>
+      <c r="K95" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L95" s="6"/>
+      <c r="M95" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N95" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O95" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P95" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q95" s="9"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A96" s="9">
+        <v>177</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E96" s="18">
+        <v>202503080258</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I96" s="6">
+        <v>1</v>
+      </c>
+      <c r="J96" s="7">
+        <v>600</v>
+      </c>
+      <c r="K96" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L96" s="6"/>
+      <c r="M96" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N96" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O96" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P96" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q96" s="9"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A97" s="9">
+        <v>178</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E97" s="18">
+        <v>202503080167</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I97" s="6">
+        <v>1</v>
+      </c>
+      <c r="J97" s="7">
+        <v>600</v>
+      </c>
+      <c r="K97" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L97" s="6"/>
+      <c r="M97" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N97" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O97" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P97" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q97" s="9"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A98" s="9">
+        <v>179</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E98" s="18">
+        <v>202503080261</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I98" s="6">
+        <v>1</v>
+      </c>
+      <c r="J98" s="7">
+        <v>600</v>
+      </c>
+      <c r="K98" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L98" s="6"/>
+      <c r="M98" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N98" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O98" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P98" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q98" s="9"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A99" s="9">
+        <v>180</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E99" s="18">
+        <v>202503080226</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I99" s="6">
+        <v>1</v>
+      </c>
+      <c r="J99" s="7">
+        <v>600</v>
+      </c>
+      <c r="K99" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L99" s="6"/>
+      <c r="M99" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N99" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O99" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P99" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q99" s="9"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A100" s="9">
+        <v>189</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E100" s="18">
+        <v>202503080269</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" s="6">
+        <v>1</v>
+      </c>
+      <c r="J100" s="7">
+        <v>600</v>
+      </c>
+      <c r="K100" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L100" s="6"/>
+      <c r="M100" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N100" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O100" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P100" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q100" s="9"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A101" s="9">
+        <v>190</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E101" s="18">
+        <v>202503080228</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I101" s="6">
+        <v>1</v>
+      </c>
+      <c r="J101" s="7">
+        <v>600</v>
+      </c>
+      <c r="K101" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L101" s="6"/>
+      <c r="M101" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N101" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O101" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P101" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q101" s="9"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A102" s="9">
+        <v>191</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E102" s="18">
+        <v>202503080121</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I102" s="6">
+        <v>1</v>
+      </c>
+      <c r="J102" s="7">
+        <v>600</v>
+      </c>
+      <c r="K102" s="11">
+        <f>Tabela1[[#This Row],[Qtd]]*Tabela1[[#This Row],[Valor]]</f>
+        <v>600</v>
+      </c>
+      <c r="L102" s="6"/>
+      <c r="M102" s="12">
+        <v>46169</v>
+      </c>
+      <c r="N102" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O102" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P102" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q102" s="9"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T1:T2" xr:uid="{3615BDC8-212A-499B-8314-77CCEF05DA1B}">
       <formula1>$T$1:$T$2</formula1>
@@ -5114,13 +6483,13 @@
           <x14:formula1>
             <xm:f>dados!$A$2:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G75</xm:sqref>
+          <xm:sqref>G2:G102</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2EFC99DB-5EC0-4498-B2A3-3B9BCA5D9123}">
           <x14:formula1>
             <xm:f>dados!$C$2:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>N2:N75</xm:sqref>
+          <xm:sqref>N2:N102</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
